--- a/GoRest接口测试用例/GoRest 接口测试用例模板.xlsx
+++ b/GoRest接口测试用例/GoRest 接口测试用例模板.xlsx
@@ -5228,7 +5228,7 @@
       <c r="P71" s="10"/>
     </row>
     <row r="72" ht="28" spans="1:16">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="9" t="s">
         <v>278</v>
       </c>
       <c r="B72" s="10" t="s">
